--- a/秋月電子購入物20270706.xlsx
+++ b/秋月電子購入物20270706.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryo/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryo/Documents/GitHub/Thrive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_A65BECE7FF40B2F4B14B8379C11D14F7671C1869" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06331E7B-D78B-EC40-B686-7FD6AC4AD556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23600" yWindow="6600" windowWidth="23600" windowHeight="15800" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OWN部品マトリクス" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
   <si>
     <r>
       <rPr>
@@ -1101,6 +1101,26 @@
       </rPr>
       <t>実装分は含まない</t>
     </r>
+  </si>
+  <si>
+    <t>toin</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <r>
+      <t>35V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>にするかも</t>
+    </r>
+    <phoneticPr fontId="10"/>
   </si>
 </sst>
 </file>
@@ -1119,7 +1139,7 @@
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1171,15 +1191,16 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="6"/>
       <name val="Tsukushi A Round Gothic Bold"/>
       <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS Gothic"/>
+      <family val="2"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -2470,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="AH13" s="12">
-        <f t="shared" ref="AH13:BM13" si="1">SUM(AH4:AH12)</f>
+        <f t="shared" ref="AH13:AY13" si="1">SUM(AH4:AH12)</f>
         <v>2</v>
       </c>
       <c r="AI13" s="12">
@@ -2540,6 +2561,17 @@
       <c r="AY13" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:51">
+      <c r="AC14" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:51">
@@ -2568,7 +2600,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11"/>
+  <phoneticPr fontId="10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
